--- a/artfynd/A 29244-2024 artfynd.xlsx
+++ b/artfynd/A 29244-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4572,6 +4572,103 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125877363</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92502</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>546442</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6958853</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29244-2024 artfynd.xlsx
+++ b/artfynd/A 29244-2024 artfynd.xlsx
@@ -4577,7 +4577,7 @@
         <v>125877363</v>
       </c>
       <c r="B39" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 29244-2024 artfynd.xlsx
+++ b/artfynd/A 29244-2024 artfynd.xlsx
@@ -4577,7 +4577,7 @@
         <v>125877363</v>
       </c>
       <c r="B39" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 29244-2024 artfynd.xlsx
+++ b/artfynd/A 29244-2024 artfynd.xlsx
@@ -4577,7 +4577,7 @@
         <v>125877363</v>
       </c>
       <c r="B39" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 29244-2024 artfynd.xlsx
+++ b/artfynd/A 29244-2024 artfynd.xlsx
@@ -4577,7 +4577,7 @@
         <v>125877363</v>
       </c>
       <c r="B39" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 29244-2024 artfynd.xlsx
+++ b/artfynd/A 29244-2024 artfynd.xlsx
@@ -4577,7 +4577,7 @@
         <v>125877363</v>
       </c>
       <c r="B39" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 29244-2024 artfynd.xlsx
+++ b/artfynd/A 29244-2024 artfynd.xlsx
@@ -4577,7 +4577,7 @@
         <v>125877363</v>
       </c>
       <c r="B39" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 29244-2024 artfynd.xlsx
+++ b/artfynd/A 29244-2024 artfynd.xlsx
@@ -4577,7 +4577,7 @@
         <v>125877363</v>
       </c>
       <c r="B39" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 29244-2024 artfynd.xlsx
+++ b/artfynd/A 29244-2024 artfynd.xlsx
@@ -4577,7 +4577,7 @@
         <v>125877363</v>
       </c>
       <c r="B39" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 29244-2024 artfynd.xlsx
+++ b/artfynd/A 29244-2024 artfynd.xlsx
@@ -4577,7 +4577,7 @@
         <v>125877363</v>
       </c>
       <c r="B39" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 29244-2024 artfynd.xlsx
+++ b/artfynd/A 29244-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110695462</v>
+        <v>119164021</v>
       </c>
       <c r="B2" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Orrlektjärn, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546589.7065298159</v>
+        <v>546375</v>
       </c>
       <c r="R2" t="n">
-        <v>6959096.553462185</v>
+        <v>6958820</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110695461</v>
+        <v>119164041</v>
       </c>
       <c r="B3" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Orrlektjärn, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546613.5773541633</v>
+        <v>546471</v>
       </c>
       <c r="R3" t="n">
-        <v>6959030.913808782</v>
+        <v>6958927</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110695454</v>
+        <v>119390828</v>
       </c>
       <c r="B4" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546353.0154499436</v>
+        <v>546677</v>
       </c>
       <c r="R4" t="n">
-        <v>6958766.51720413</v>
+        <v>6959109</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110695472</v>
+        <v>109324932</v>
       </c>
       <c r="B5" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Orrlektjärnen, S, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546481.5578312263</v>
+        <v>546275</v>
       </c>
       <c r="R5" t="n">
-        <v>6959022.173667082</v>
+        <v>6958753</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110695456</v>
+        <v>119164094</v>
       </c>
       <c r="B6" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Orrlektjärn, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546368.3690143349</v>
+        <v>546482</v>
       </c>
       <c r="R6" t="n">
-        <v>6958816.678937944</v>
+        <v>6958984</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,27 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110695474</v>
+        <v>119164096</v>
       </c>
       <c r="B7" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Orrlektjärn, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546481.5578312263</v>
+        <v>546520</v>
       </c>
       <c r="R7" t="n">
-        <v>6959022.173667082</v>
+        <v>6959008</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,22 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,27 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110695457</v>
+        <v>119164098</v>
       </c>
       <c r="B8" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Orrlektjärn, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546457.1306711356</v>
+        <v>546632</v>
       </c>
       <c r="R8" t="n">
-        <v>6958834.88451552</v>
+        <v>6959007</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,22 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,27 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110695473</v>
+        <v>119164100</v>
       </c>
       <c r="B9" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,34 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Orrlektjärn, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546481.5578312263</v>
+        <v>546513</v>
       </c>
       <c r="R9" t="n">
-        <v>6959022.173667082</v>
+        <v>6958941</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,22 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,62 +1439,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110695458</v>
+        <v>119164102</v>
       </c>
       <c r="B10" t="n">
-        <v>78536</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Orrlektjärn, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546457.1306711356</v>
+        <v>546483</v>
       </c>
       <c r="R10" t="n">
-        <v>6958834.88451552</v>
+        <v>6958923</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,22 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,27 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110695455</v>
+        <v>119164104</v>
       </c>
       <c r="B11" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Orrlektjärn, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546368.3690143349</v>
+        <v>546459</v>
       </c>
       <c r="R11" t="n">
-        <v>6958816.678937944</v>
+        <v>6958928</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,22 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,27 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110695460</v>
+        <v>125877363</v>
       </c>
       <c r="B12" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,13 +1680,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546648.7401515668</v>
+        <v>546442</v>
       </c>
       <c r="R12" t="n">
-        <v>6959010.335581302</v>
+        <v>6958853</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1865,22 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,62 +1730,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119164096</v>
+        <v>110695455</v>
       </c>
       <c r="B13" t="n">
-        <v>91838</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Orrlektjärn, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546520</v>
+        <v>546368</v>
       </c>
       <c r="R13" t="n">
-        <v>6959008</v>
+        <v>6958817</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,62 +1827,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119164051</v>
+        <v>110695462</v>
       </c>
       <c r="B14" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Orrlektjärn, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546409</v>
+        <v>546590</v>
       </c>
       <c r="R14" t="n">
-        <v>6958919</v>
+        <v>6959096</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2099,62 +1924,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119164060</v>
+        <v>110695472</v>
       </c>
       <c r="B15" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Orrlektjärn, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546593</v>
+        <v>546482</v>
       </c>
       <c r="R15" t="n">
-        <v>6959088</v>
+        <v>6959022</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2181,12 +2001,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,62 +2021,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119164072</v>
+        <v>110695474</v>
       </c>
       <c r="B16" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Orrlektjärn, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546620</v>
+        <v>546482</v>
       </c>
       <c r="R16" t="n">
-        <v>6959041</v>
+        <v>6959022</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2283,12 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2303,62 +2118,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119164078</v>
+        <v>110695454</v>
       </c>
       <c r="B17" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Orrlektjärn, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546592</v>
+        <v>546353</v>
       </c>
       <c r="R17" t="n">
-        <v>6958955</v>
+        <v>6958766</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2385,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2405,27 +2215,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119164024</v>
+        <v>110695456</v>
       </c>
       <c r="B18" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,34 +2238,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Orrlektjärn, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546412</v>
+        <v>546368</v>
       </c>
       <c r="R18" t="n">
-        <v>6958871</v>
+        <v>6958817</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,17 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2512,27 +2312,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119164021</v>
+        <v>110695457</v>
       </c>
       <c r="B19" t="n">
-        <v>90560</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2540,34 +2335,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Orrlektjärn, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546375</v>
+        <v>546457</v>
       </c>
       <c r="R19" t="n">
-        <v>6958820</v>
+        <v>6958835</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2594,12 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2614,62 +2409,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119164068</v>
+        <v>110695460</v>
       </c>
       <c r="B20" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Orrlektjärn, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546615</v>
+        <v>546649</v>
       </c>
       <c r="R20" t="n">
-        <v>6959075</v>
+        <v>6959010</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,12 +2486,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2716,62 +2506,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119164082</v>
+        <v>110695461</v>
       </c>
       <c r="B21" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Orrlektjärn, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546375</v>
+        <v>546613</v>
       </c>
       <c r="R21" t="n">
-        <v>6958806</v>
+        <v>6959031</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,12 +2583,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2818,49 +2603,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119164076</v>
+        <v>119164049</v>
       </c>
       <c r="B22" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546637</v>
+        <v>546426</v>
       </c>
       <c r="R22" t="n">
-        <v>6958963</v>
+        <v>6958927</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,15 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119164033</v>
+        <v>119164051</v>
       </c>
       <c r="B23" t="n">
-        <v>91882</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2948,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5449</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2972,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546482</v>
+        <v>546409</v>
       </c>
       <c r="R23" t="n">
-        <v>6958990</v>
+        <v>6958919</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,15 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119164026</v>
+        <v>119164022</v>
       </c>
       <c r="B24" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3074,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546411</v>
+        <v>546408</v>
       </c>
       <c r="R24" t="n">
-        <v>6958870</v>
+        <v>6958919</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3114,7 +2884,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3141,37 +2911,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119164064</v>
+        <v>119164024</v>
       </c>
       <c r="B25" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3181,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546491</v>
+        <v>546412</v>
       </c>
       <c r="R25" t="n">
-        <v>6959044</v>
+        <v>6958871</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3217,6 +2982,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,37 +3013,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119164100</v>
+        <v>119164026</v>
       </c>
       <c r="B26" t="n">
-        <v>91838</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3283,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546513</v>
+        <v>546411</v>
       </c>
       <c r="R26" t="n">
-        <v>6958941</v>
+        <v>6958870</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3319,6 +3084,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,53 +3115,56 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119164080</v>
+        <v>119396765</v>
       </c>
       <c r="B27" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Orrlektjärn, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>546386</v>
+        <v>546677</v>
       </c>
       <c r="R27" t="n">
-        <v>6958845</v>
+        <v>6959109</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3415,12 +3188,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3435,65 +3208,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119164062</v>
+        <v>110695453</v>
       </c>
       <c r="B28" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Orrlektjärn, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546600</v>
+        <v>546356</v>
       </c>
       <c r="R28" t="n">
-        <v>6959075</v>
+        <v>6958739</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3517,12 +3285,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3537,27 +3305,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119164094</v>
+        <v>125877289</v>
       </c>
       <c r="B29" t="n">
-        <v>91838</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3565,37 +3328,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>219880</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Orrlektjärn, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546482</v>
+        <v>546667</v>
       </c>
       <c r="R29" t="n">
-        <v>6958984</v>
+        <v>6958930</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3619,12 +3382,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3639,49 +3402,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119164035</v>
+        <v>119164056</v>
       </c>
       <c r="B30" t="n">
-        <v>91882</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3691,10 +3449,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546513</v>
+        <v>546502</v>
       </c>
       <c r="R30" t="n">
-        <v>6958949</v>
+        <v>6959119</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3753,15 +3511,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119164070</v>
+        <v>119164058</v>
       </c>
       <c r="B31" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3793,10 +3546,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546613</v>
+        <v>546637</v>
       </c>
       <c r="R31" t="n">
-        <v>6959051</v>
+        <v>6959109</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3855,37 +3608,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119164049</v>
+        <v>119164060</v>
       </c>
       <c r="B32" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,10 +3643,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546426</v>
+        <v>546593</v>
       </c>
       <c r="R32" t="n">
-        <v>6958927</v>
+        <v>6959088</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3957,15 +3705,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119164058</v>
+        <v>119164062</v>
       </c>
       <c r="B33" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3997,10 +3740,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546637</v>
+        <v>546600</v>
       </c>
       <c r="R33" t="n">
-        <v>6959109</v>
+        <v>6959075</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4059,37 +3802,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119164098</v>
+        <v>119164064</v>
       </c>
       <c r="B34" t="n">
-        <v>91838</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4099,10 +3837,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>546632</v>
+        <v>546491</v>
       </c>
       <c r="R34" t="n">
-        <v>6959007</v>
+        <v>6959044</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4161,37 +3899,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119164022</v>
+        <v>119164066</v>
       </c>
       <c r="B35" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4201,10 +3934,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546408</v>
+        <v>546468</v>
       </c>
       <c r="R35" t="n">
-        <v>6958919</v>
+        <v>6959036</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4237,11 +3970,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4268,37 +3996,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119164104</v>
+        <v>119164068</v>
       </c>
       <c r="B36" t="n">
-        <v>91838</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4308,10 +4031,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546459</v>
+        <v>546615</v>
       </c>
       <c r="R36" t="n">
-        <v>6958928</v>
+        <v>6959075</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4370,37 +4093,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119164102</v>
+        <v>119164070</v>
       </c>
       <c r="B37" t="n">
-        <v>91838</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4410,10 +4128,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>546483</v>
+        <v>546613</v>
       </c>
       <c r="R37" t="n">
-        <v>6958923</v>
+        <v>6959051</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4472,37 +4190,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119164041</v>
+        <v>119164072</v>
       </c>
       <c r="B38" t="n">
-        <v>91830</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4512,10 +4225,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>546471</v>
+        <v>546620</v>
       </c>
       <c r="R38" t="n">
-        <v>6958927</v>
+        <v>6959041</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4574,48 +4287,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125877363</v>
+        <v>119164074</v>
       </c>
       <c r="B39" t="n">
-        <v>92535</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Orrlektjärn, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>546442</v>
+        <v>546691</v>
       </c>
       <c r="R39" t="n">
-        <v>6958853</v>
+        <v>6959009</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4639,12 +4352,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4659,15 +4372,791 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>119164076</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Orrlektjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>546637</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6958963</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>119164078</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Orrlektjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>546592</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6958955</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>119164080</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Orrlektjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>546386</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6958845</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>119164082</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Orrlektjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>546375</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6958806</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>119390827</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>546670</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6959110</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>110695452</v>
+      </c>
+      <c r="B45" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>546356</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6958739</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>110695473</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>546482</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6959022</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>110695458</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>546457</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6958835</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29244-2024 artfynd.xlsx
+++ b/artfynd/A 29244-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164021</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164041</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119390828</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109324932</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164094</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164096</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164098</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164100</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164102</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164104</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877363</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110695455</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110695462</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110695472</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110695474</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110695454</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110695456</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110695457</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110695460</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110695461</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164049</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164051</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2908,6 +3023,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164022</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3010,6 +3130,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3112,6 +3237,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164026</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3217,6 +3347,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119396765</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3314,6 +3449,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110695453</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3411,6 +3551,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877289</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3508,6 +3653,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164056</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3605,6 +3755,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164058</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3702,6 +3857,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164060</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3799,6 +3959,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164062</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3896,6 +4061,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164064</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3993,6 +4163,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164066</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4090,6 +4265,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164068</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4187,6 +4367,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164070</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4284,6 +4469,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164072</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4381,6 +4571,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164074</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4478,6 +4673,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164076</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4575,6 +4775,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164078</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4672,6 +4877,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164080</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4769,6 +4979,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164082</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4866,6 +5081,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119390827</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4963,6 +5183,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110695452</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5060,6 +5285,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110695473</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5157,8 +5387,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110695458</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>